--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="228">
   <si>
     <t>App</t>
   </si>
@@ -658,6 +658,12 @@
   </si>
   <si>
     <t>C70877</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70878</t>
   </si>
   <si>
     <t>Name</t>
@@ -1773,16 +1779,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G160"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetPr/>
+  <dimension ref="A1:H160"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
     <col min="7" max="7" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1805,7 +1811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
@@ -1828,7 +1834,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="11" t="s">
         <v>7</v>
       </c>
@@ -1848,10 +1854,13 @@
         <v>12</v>
       </c>
       <c r="G3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
@@ -1871,10 +1880,13 @@
         <v>12</v>
       </c>
       <c r="G4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="11" t="s">
         <v>7</v>
       </c>
@@ -1897,7 +1909,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" s="11" t="s">
         <v>7</v>
       </c>
@@ -1920,7 +1932,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" s="11" t="s">
         <v>7</v>
       </c>
@@ -1943,7 +1955,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -1966,7 +1978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -1989,7 +2001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
@@ -2012,7 +2024,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11" s="11" t="s">
         <v>7</v>
       </c>
@@ -2032,10 +2044,13 @@
         <v>12</v>
       </c>
       <c r="G11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="1" hidden="1" spans="1:7">
+    <row r="12" customFormat="1" spans="1:8">
       <c r="A12" s="11" t="s">
         <v>7</v>
       </c>
@@ -2055,10 +2070,10 @@
         <v>12</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" hidden="1" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="11" t="s">
         <v>7</v>
       </c>
@@ -2078,10 +2093,10 @@
         <v>12</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" hidden="1" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="11" t="s">
         <v>7</v>
       </c>
@@ -2101,10 +2116,10 @@
         <v>12</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" hidden="1" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="11" t="s">
         <v>7</v>
       </c>
@@ -2127,7 +2142,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16" s="11" t="s">
         <v>7</v>
       </c>
@@ -2147,10 +2162,13 @@
         <v>12</v>
       </c>
       <c r="G16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:7">
+    <row r="17" spans="1:8">
       <c r="A17" s="11" t="s">
         <v>7</v>
       </c>
@@ -2173,7 +2191,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:7">
+    <row r="18" spans="1:8">
       <c r="A18" s="11" t="s">
         <v>7</v>
       </c>
@@ -2193,10 +2211,13 @@
         <v>12</v>
       </c>
       <c r="G18" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:7">
+    <row r="19" spans="1:8">
       <c r="A19" s="11" t="s">
         <v>7</v>
       </c>
@@ -2219,7 +2240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:8">
       <c r="A20" s="11" t="s">
         <v>7</v>
       </c>
@@ -2242,7 +2263,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:7">
+    <row r="21" spans="1:8">
       <c r="A21" s="11" t="s">
         <v>7</v>
       </c>
@@ -2265,7 +2286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:7">
+    <row r="22" spans="1:8">
       <c r="A22" s="11" t="s">
         <v>7</v>
       </c>
@@ -2288,7 +2309,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:7">
+    <row r="23" spans="1:8">
       <c r="A23" s="11" t="s">
         <v>7</v>
       </c>
@@ -2311,7 +2332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:7">
+    <row r="24" spans="1:8">
       <c r="A24" s="11" t="s">
         <v>7</v>
       </c>
@@ -2334,7 +2355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:7">
+    <row r="25" spans="1:8">
       <c r="A25" s="11" t="s">
         <v>7</v>
       </c>
@@ -2357,7 +2378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:7">
+    <row r="26" spans="1:8">
       <c r="A26" s="11" t="s">
         <v>7</v>
       </c>
@@ -2377,10 +2398,13 @@
         <v>12</v>
       </c>
       <c r="G26" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:7">
+    <row r="27" spans="1:8">
       <c r="A27" s="11" t="s">
         <v>7</v>
       </c>
@@ -2400,10 +2424,13 @@
         <v>12</v>
       </c>
       <c r="G27" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:7">
+    <row r="28" spans="1:8">
       <c r="A28" s="11" t="s">
         <v>7</v>
       </c>
@@ -2423,10 +2450,13 @@
         <v>12</v>
       </c>
       <c r="G28" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:7">
+    <row r="29" spans="1:8">
       <c r="A29" s="11" t="s">
         <v>7</v>
       </c>
@@ -2448,8 +2478,9 @@
       <c r="G29" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" hidden="1" spans="1:7">
+      <c r="H29" s="11"/>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="11" t="s">
         <v>7</v>
       </c>
@@ -2469,10 +2500,13 @@
         <v>12</v>
       </c>
       <c r="G30" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:7">
+    <row r="31" spans="1:8">
       <c r="A31" s="11" t="s">
         <v>7</v>
       </c>
@@ -2492,10 +2526,10 @@
         <v>12</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" hidden="1" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="11" t="s">
         <v>7</v>
       </c>
@@ -2518,7 +2552,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:7">
+    <row r="33" spans="1:8">
       <c r="A33" s="11" t="s">
         <v>7</v>
       </c>
@@ -2538,10 +2572,13 @@
         <v>12</v>
       </c>
       <c r="G33" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:7">
+    <row r="34" spans="1:8">
       <c r="A34" s="11" t="s">
         <v>7</v>
       </c>
@@ -2561,10 +2598,13 @@
         <v>12</v>
       </c>
       <c r="G34" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:7">
+    <row r="35" spans="1:8">
       <c r="A35" s="11" t="s">
         <v>7</v>
       </c>
@@ -2584,10 +2624,13 @@
         <v>12</v>
       </c>
       <c r="G35" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="36" customFormat="1" spans="1:7">
+    <row r="36" customFormat="1" spans="1:8">
       <c r="A36" s="11" t="s">
         <v>7</v>
       </c>
@@ -2610,7 +2653,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:7">
+    <row r="37" spans="1:8">
       <c r="A37" s="11" t="s">
         <v>7</v>
       </c>
@@ -2630,10 +2673,13 @@
         <v>12</v>
       </c>
       <c r="G37" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:7">
+    <row r="38" spans="1:8">
       <c r="A38" s="11" t="s">
         <v>7</v>
       </c>
@@ -2656,7 +2702,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:7">
+    <row r="39" spans="1:8">
       <c r="A39" s="11" t="s">
         <v>7</v>
       </c>
@@ -2679,7 +2725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:7">
+    <row r="40" spans="1:8">
       <c r="A40" s="11" t="s">
         <v>7</v>
       </c>
@@ -2699,10 +2745,13 @@
         <v>12</v>
       </c>
       <c r="G40" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:8">
       <c r="A41" s="11" t="s">
         <v>7</v>
       </c>
@@ -2725,7 +2774,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" customFormat="1" hidden="1" spans="1:7">
+    <row r="42" customFormat="1" spans="1:8">
       <c r="A42" s="11" t="s">
         <v>7</v>
       </c>
@@ -2745,10 +2794,13 @@
         <v>12</v>
       </c>
       <c r="G42" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:7">
+    <row r="43" spans="1:8">
       <c r="A43" s="11" t="s">
         <v>7</v>
       </c>
@@ -2768,10 +2820,13 @@
         <v>12</v>
       </c>
       <c r="G43" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:7">
+    <row r="44" spans="1:8">
       <c r="A44" s="11" t="s">
         <v>7</v>
       </c>
@@ -2794,7 +2849,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:7">
+    <row r="45" spans="1:8">
       <c r="A45" s="11" t="s">
         <v>7</v>
       </c>
@@ -2814,10 +2869,13 @@
         <v>12</v>
       </c>
       <c r="G45" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:7">
+    <row r="46" spans="1:8">
       <c r="A46" s="11" t="s">
         <v>7</v>
       </c>
@@ -2837,10 +2895,13 @@
         <v>12</v>
       </c>
       <c r="G46" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:7">
+    <row r="47" spans="1:8">
       <c r="A47" s="11" t="s">
         <v>7</v>
       </c>
@@ -2860,10 +2921,13 @@
         <v>12</v>
       </c>
       <c r="G47" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:7">
+    <row r="48" spans="1:8">
       <c r="A48" s="11" t="s">
         <v>7</v>
       </c>
@@ -2883,10 +2947,13 @@
         <v>12</v>
       </c>
       <c r="G48" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:7">
+    <row r="49" spans="1:8">
       <c r="A49" s="11" t="s">
         <v>7</v>
       </c>
@@ -2906,10 +2973,13 @@
         <v>12</v>
       </c>
       <c r="G49" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:7">
+    <row r="50" spans="1:8">
       <c r="A50" s="11" t="s">
         <v>7</v>
       </c>
@@ -2929,10 +2999,13 @@
         <v>12</v>
       </c>
       <c r="G50" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:8">
       <c r="A51" s="11" t="s">
         <v>7</v>
       </c>
@@ -2952,10 +3025,13 @@
         <v>12</v>
       </c>
       <c r="G51" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:7">
+    <row r="52" spans="1:8">
       <c r="A52" s="11" t="s">
         <v>7</v>
       </c>
@@ -2978,7 +3054,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:7">
+    <row r="53" spans="1:8">
       <c r="A53" s="11" t="s">
         <v>7</v>
       </c>
@@ -2998,10 +3074,13 @@
         <v>12</v>
       </c>
       <c r="G53" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:7">
+    <row r="54" spans="1:8">
       <c r="A54" s="11" t="s">
         <v>7</v>
       </c>
@@ -3024,7 +3103,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:7">
+    <row r="55" spans="1:8">
       <c r="A55" s="11" t="s">
         <v>7</v>
       </c>
@@ -3044,10 +3123,13 @@
         <v>12</v>
       </c>
       <c r="G55" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:7">
+    <row r="56" spans="1:8">
       <c r="A56" s="11" t="s">
         <v>7</v>
       </c>
@@ -3067,10 +3149,13 @@
         <v>12</v>
       </c>
       <c r="G56" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:7">
+    <row r="57" spans="1:8">
       <c r="A57" s="11" t="s">
         <v>7</v>
       </c>
@@ -3090,10 +3175,13 @@
         <v>12</v>
       </c>
       <c r="G57" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:7">
+    <row r="58" spans="1:8">
       <c r="A58" s="11" t="s">
         <v>7</v>
       </c>
@@ -3116,7 +3204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:7">
+    <row r="59" spans="1:8">
       <c r="A59" s="11" t="s">
         <v>7</v>
       </c>
@@ -3136,10 +3224,13 @@
         <v>12</v>
       </c>
       <c r="G59" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:7">
+    <row r="60" spans="1:8">
       <c r="A60" s="11" t="s">
         <v>7</v>
       </c>
@@ -3159,10 +3250,13 @@
         <v>12</v>
       </c>
       <c r="G60" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:7">
+    <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -3182,10 +3276,13 @@
         <v>12</v>
       </c>
       <c r="G61" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:7">
+    <row r="62" spans="1:8">
       <c r="A62" s="11" t="s">
         <v>7</v>
       </c>
@@ -3208,7 +3305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:7">
+    <row r="63" spans="1:8">
       <c r="A63" s="11" t="s">
         <v>7</v>
       </c>
@@ -3231,7 +3328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:7">
+    <row r="64" spans="1:8">
       <c r="A64" s="11" t="s">
         <v>7</v>
       </c>
@@ -3251,10 +3348,13 @@
         <v>12</v>
       </c>
       <c r="G64" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:7">
+    <row r="65" spans="1:8">
       <c r="A65" s="11" t="s">
         <v>7</v>
       </c>
@@ -3274,10 +3374,13 @@
         <v>12</v>
       </c>
       <c r="G65" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:7">
+    <row r="66" spans="1:8">
       <c r="A66" s="11" t="s">
         <v>7</v>
       </c>
@@ -3297,10 +3400,13 @@
         <v>12</v>
       </c>
       <c r="G66" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:7">
+    <row r="67" spans="1:8">
       <c r="A67" s="11" t="s">
         <v>7</v>
       </c>
@@ -3320,10 +3426,13 @@
         <v>12</v>
       </c>
       <c r="G67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:7">
+    <row r="68" spans="1:8">
       <c r="A68" s="11" t="s">
         <v>7</v>
       </c>
@@ -3343,10 +3452,13 @@
         <v>12</v>
       </c>
       <c r="G68" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:7">
+    <row r="69" spans="1:8">
       <c r="A69" s="11" t="s">
         <v>7</v>
       </c>
@@ -3366,10 +3478,13 @@
         <v>12</v>
       </c>
       <c r="G69" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:7">
+    <row r="70" spans="1:8">
       <c r="A70" s="11" t="s">
         <v>7</v>
       </c>
@@ -3389,10 +3504,13 @@
         <v>12</v>
       </c>
       <c r="G70" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:7">
+    <row r="71" spans="1:8">
       <c r="A71" s="11" t="s">
         <v>7</v>
       </c>
@@ -3412,10 +3530,13 @@
         <v>12</v>
       </c>
       <c r="G71" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:7">
+    <row r="72" spans="1:8">
       <c r="A72" s="11" t="s">
         <v>7</v>
       </c>
@@ -3435,10 +3556,13 @@
         <v>12</v>
       </c>
       <c r="G72" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:7">
+    <row r="73" spans="1:8">
       <c r="A73" s="11" t="s">
         <v>7</v>
       </c>
@@ -3458,10 +3582,13 @@
         <v>12</v>
       </c>
       <c r="G73" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:7">
+    <row r="74" spans="1:8">
       <c r="A74" s="11" t="s">
         <v>7</v>
       </c>
@@ -3481,10 +3608,13 @@
         <v>12</v>
       </c>
       <c r="G74" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:7">
+    <row r="75" spans="1:8">
       <c r="A75" s="11" t="s">
         <v>7</v>
       </c>
@@ -3504,10 +3634,13 @@
         <v>12</v>
       </c>
       <c r="G75" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:7">
+    <row r="76" spans="1:8">
       <c r="A76" s="11" t="s">
         <v>7</v>
       </c>
@@ -3530,7 +3663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:7">
+    <row r="77" spans="1:8">
       <c r="A77" s="11" t="s">
         <v>7</v>
       </c>
@@ -3550,10 +3683,13 @@
         <v>12</v>
       </c>
       <c r="G77" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:7">
+    <row r="78" spans="1:8">
       <c r="A78" s="11" t="s">
         <v>7</v>
       </c>
@@ -3573,10 +3709,13 @@
         <v>12</v>
       </c>
       <c r="G78" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:7">
+    <row r="79" spans="1:8">
       <c r="A79" s="11" t="s">
         <v>7</v>
       </c>
@@ -3596,10 +3735,13 @@
         <v>12</v>
       </c>
       <c r="G79" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:7">
+    <row r="80" spans="1:8">
       <c r="A80" s="11" t="s">
         <v>7</v>
       </c>
@@ -3619,10 +3761,10 @@
         <v>12</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" hidden="1" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="11" t="s">
         <v>7</v>
       </c>
@@ -3645,7 +3787,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:7">
+    <row r="82" spans="1:8">
       <c r="A82" s="11" t="s">
         <v>7</v>
       </c>
@@ -3665,10 +3807,13 @@
         <v>12</v>
       </c>
       <c r="G82" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:7">
+    <row r="83" spans="1:8">
       <c r="A83" s="11" t="s">
         <v>7</v>
       </c>
@@ -3691,7 +3836,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:7">
+    <row r="84" spans="1:8">
       <c r="A84" s="11" t="s">
         <v>7</v>
       </c>
@@ -3714,7 +3859,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:7">
+    <row r="85" spans="1:8">
       <c r="A85" s="11" t="s">
         <v>7</v>
       </c>
@@ -3737,7 +3882,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:7">
+    <row r="86" spans="1:8">
       <c r="A86" s="11" t="s">
         <v>7</v>
       </c>
@@ -3760,7 +3905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:7">
+    <row r="87" spans="1:8">
       <c r="A87" s="11" t="s">
         <v>7</v>
       </c>
@@ -3783,7 +3928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:8">
       <c r="A88" s="11" t="s">
         <v>7</v>
       </c>
@@ -3806,7 +3951,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:7">
+    <row r="89" spans="1:8">
       <c r="A89" s="11" t="s">
         <v>7</v>
       </c>
@@ -3829,7 +3974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:7">
+    <row r="90" spans="1:8">
       <c r="A90" s="11" t="s">
         <v>7</v>
       </c>
@@ -3852,7 +3997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:7">
+    <row r="91" spans="1:8">
       <c r="A91" s="11" t="s">
         <v>7</v>
       </c>
@@ -3875,7 +4020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:8">
       <c r="A92" s="11" t="s">
         <v>7</v>
       </c>
@@ -3898,7 +4043,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:8">
       <c r="A93" s="11" t="s">
         <v>7</v>
       </c>
@@ -3921,7 +4066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:8">
       <c r="A94" s="11" t="s">
         <v>7</v>
       </c>
@@ -3944,7 +4089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:8">
       <c r="A95" s="11" t="s">
         <v>7</v>
       </c>
@@ -3967,7 +4112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:8">
       <c r="A96" s="11" t="s">
         <v>7</v>
       </c>
@@ -4013,7 +4158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:7">
+    <row r="98" spans="1:7">
       <c r="A98" s="11" t="s">
         <v>7</v>
       </c>
@@ -4036,7 +4181,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:7">
+    <row r="99" spans="1:7">
       <c r="A99" s="11" t="s">
         <v>7</v>
       </c>
@@ -4060,12 +4205,27 @@
       </c>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="11"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="15"/>
+      <c r="A100" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="11"/>
@@ -4548,22 +4708,7 @@
       <c r="F160" s="15"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G99" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Current_Foreign_Account"/>
-        <filter val="Current_Foreign_Accounts-Product_Details-Financial-Details_Is_Not_Visible_[MOB_ANDROID]"/>
-        <filter val="Current_Foreign_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]"/>
-        <filter val="Current_Foreign-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]"/>
-        <filter val="Current_Foreign_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]"/>
-        <filter val="Current_Foreign_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]"/>
-        <filter val="Product_Summary-Current_Foreign_Accounts_List_[MOB_ANDROID]"/>
-        <filter val="Current_Foreign_Account-Transactions-Filter_By_Type_[MOB_ANDROID]"/>
-        <filter val="CURRENT_FOREIGN_ACCOUNTS-TRANSACTIONS-OVERVIEW_BY_DIFFERENT_CURRENCIES_[MOB_ANDROID]"/>
-        <filter val="Current_Foreign_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]"/>
-        <filter val="Current_Foreign_Accounts_Product_Details_Account_Details_[MOB_ANDROID]"/>
-      </filters>
-    </filterColumn>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G100" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -4589,16 +4734,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -4606,10 +4751,10 @@
         <v>179</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
@@ -4617,13 +4762,13 @@
         <v>205</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
@@ -4631,10 +4776,10 @@
         <v>181</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
@@ -4642,10 +4787,10 @@
         <v>85</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
@@ -4653,10 +4798,10 @@
         <v>183</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="D6" s="5"/>
     </row>
@@ -4665,13 +4810,13 @@
         <v>185</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -4679,10 +4824,10 @@
         <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
@@ -4690,10 +4835,10 @@
         <v>67</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
@@ -4701,10 +4846,10 @@
         <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D10" s="7"/>
     </row>
@@ -4713,10 +4858,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:4">
@@ -4724,10 +4869,10 @@
         <v>73</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:4">
@@ -4735,10 +4880,10 @@
         <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:4">
@@ -4746,10 +4891,10 @@
         <v>87</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:4">
@@ -4757,10 +4902,10 @@
         <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:4">
@@ -4768,13 +4913,13 @@
         <v>189</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:4">
@@ -4782,10 +4927,10 @@
         <v>191</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D17" s="9"/>
     </row>
@@ -4794,10 +4939,10 @@
         <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:4">
@@ -4805,24 +4950,24 @@
         <v>117</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:4">
@@ -4830,10 +4975,10 @@
         <v>81</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:4">
@@ -4841,21 +4986,21 @@
         <v>161</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:4">
       <c r="A23" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:4">
@@ -4863,10 +5008,10 @@
         <v>171</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:4">
@@ -4874,10 +5019,10 @@
         <v>113</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:4">
@@ -4885,10 +5030,10 @@
         <v>135</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:4">
@@ -4896,10 +5041,10 @@
         <v>97</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:4">
@@ -4907,10 +5052,10 @@
         <v>125</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:4">
@@ -4918,10 +5063,10 @@
         <v>175</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:4">
@@ -4929,10 +5074,10 @@
         <v>177</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:4">
@@ -4940,10 +5085,10 @@
         <v>207</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D31" s="7"/>
     </row>
@@ -4952,13 +5097,13 @@
         <v>193</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:4">
@@ -4966,10 +5111,10 @@
         <v>195</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D33" s="7"/>
     </row>
@@ -4978,10 +5123,10 @@
         <v>197</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:4">
@@ -4989,10 +5134,10 @@
         <v>199</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:4">
@@ -5000,10 +5145,10 @@
         <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:4">
@@ -5011,10 +5156,10 @@
         <v>201</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:4">
@@ -5022,10 +5167,10 @@
         <v>19</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:4">
@@ -5033,10 +5178,10 @@
         <v>203</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="245">
   <si>
     <t>App</t>
   </si>
@@ -294,406 +294,457 @@
     <t>C70816</t>
   </si>
   <si>
+    <t>Term_Deposits_Accounts-Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70817</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70818</t>
+  </si>
+  <si>
+    <t>Product_Summary-Current_Foreign_Accounts_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70819</t>
+  </si>
+  <si>
+    <t>Manage_Products-Hide/Show_account_on_Product_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70820</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70821</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Cancel_Button_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70822</t>
+  </si>
+  <si>
+    <t>Credit_cards_transactions_filter_by_date-Date_Picker_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70823</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Filter_Date_Picker_invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70824</t>
+  </si>
+  <si>
+    <t>Credit_cards-Transactions-Filter-Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70825</t>
+  </si>
+  <si>
+    <t>Credit_cards-Transactions-Filter-Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70826</t>
+  </si>
+  <si>
+    <t>Credit_cards-Transactions-Filter-Filter_By_Amount_invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70827</t>
+  </si>
+  <si>
+    <t>Product_Summary-Term_Deposit_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70828</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Product_Details_Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70829</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer-Flow_Disruption_Cancel/Back_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70830</t>
+  </si>
+  <si>
+    <t>Credit_cards-Transactions-Filter_Multiple_Filter_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70831</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-Camera_Permission_Reject_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70832</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70833</t>
+  </si>
+  <si>
+    <t>Products-Current_Account-Cheques_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70834</t>
+  </si>
+  <si>
+    <t>Products-Current_Account-Cheques-Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70835</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Back_Button_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70836</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Filter-Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70837</t>
+  </si>
+  <si>
+    <t>Products-Current_Account-Cheques-Input_Fields-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70838</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Create_New_Recipient_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70839</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Modify_Data_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70840</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-In_Future_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70841</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_DATE_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70842</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_DATE-invalid_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70843</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_AMOUNT_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70844</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_AMOUNT-invalid_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70845</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_STATUS_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70846</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Product_On_The_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70847</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70848</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Details-Financial_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70849</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70850</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70851</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70852</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70853</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70854</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70855</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-CREATE_CONFIRMATION_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70856</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Payments_Transaction_List_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70857</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Details-Financial_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70858</t>
+  </si>
+  <si>
+    <t>Authentication-Mobile_Login-Logout_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70859</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-Successful_Payment_Via_The_Scan_And_Pay_Option_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70860</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-QR_Code_Not_Recognized_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70861</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-Payment_Via_The_Scan_And_Pay_Option-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70862</t>
+  </si>
+  <si>
+    <t>Mobile_Login-Generate_OTP-mToken_From_Login_Screen_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70863</t>
+  </si>
+  <si>
+    <t>Term_Deposit_Accounts_Details_Financial_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70864</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Confirmation_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70865</t>
+  </si>
+  <si>
+    <t>CURRENT_FOREIGN_ACCOUNTS-TRANSACTIONS-OVERVIEW_BY_DIFFERENT_CURRENCIES_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70866</t>
+  </si>
+  <si>
+    <t>General-Login_Page_Elements-Buttons-Activated_Users_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70867</t>
+  </si>
+  <si>
+    <t>Authentication-Login_In_MOB-Login_Page_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70868</t>
+  </si>
+  <si>
+    <t>Authentication-Login_With_PIN_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70869</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70870</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70871</t>
+  </si>
+  <si>
+    <t>Current_Foreign-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70872</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70873</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70874</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70875</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70876</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Input-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70877</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70878</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70879</t>
+  </si>
+  <si>
+    <t>CURRENT_ACCOUNTS_RSD-STATEMANTS-FILTER_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70880</t>
+  </si>
+  <si>
+    <t>CURRENT_FOREIGN_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70881</t>
+  </si>
+  <si>
+    <t>SAVINGS_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70882</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-Invalid_Account_Combination_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70883</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-Domestic_Payment_Page_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70884</t>
+  </si>
+  <si>
+    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Debit_Cards</t>
+  </si>
+  <si>
+    <t>C70885</t>
+  </si>
+  <si>
+    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70886</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Okruzenje</t>
+  </si>
+  <si>
+    <t>Napomena</t>
+  </si>
+  <si>
+    <t>Sanity</t>
+  </si>
+  <si>
+    <t>UAT</t>
+  </si>
+  <si>
+    <t>Oba</t>
+  </si>
+  <si>
+    <t>Pusti test kada proradi placanje da vidis je l rade poslednji koraci</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Poslednji korak pada. Kada kliknem na drugu valutu, ostaje transakcija sa EUR valutom</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Term_Deposits_Accounts_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70817</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70818</t>
-  </si>
-  <si>
-    <t>Product_Summary-Current_Foreign_Accounts_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70819</t>
-  </si>
-  <si>
-    <t>Manage_Products-Hide/Show_account_on_Product_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70820</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70821</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Cancel_Button_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70822</t>
-  </si>
-  <si>
-    <t>Credit_cards_transactions_filter_by_date-Date_Picker_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70823</t>
-  </si>
-  <si>
-    <t>Credit_cards_transactions_filter_invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70824</t>
-  </si>
-  <si>
-    <t>Credit_cards-Transactions-Filter-Filter_By_Type_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70825</t>
-  </si>
-  <si>
-    <t>Credit_cards-Transactions-Filter-Filter_By_Amount_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70826</t>
-  </si>
-  <si>
-    <t>Credit_cards-Transactions-Filter-Filter_By_Amount_invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70827</t>
-  </si>
-  <si>
-    <t>Product_Summary-Term_Deposit_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70828</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts_Product_Details_Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70829</t>
-  </si>
-  <si>
-    <t>Payments_Own_Account_Transfer-Flow_Disruption_Cancel/Back_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70830</t>
-  </si>
-  <si>
-    <t>Credit_cards-Transactions-Filter_Multiple_Filter_Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70831</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-Camera_Permission_Reject_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70832</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70833</t>
-  </si>
-  <si>
-    <t>Products-Current_Account-Cheques_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70834</t>
-  </si>
-  <si>
-    <t>Products-Current_Account-Cheques-Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70835</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Back_Button_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70836</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions-Filter-Filter_By_Amount_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70837</t>
-  </si>
-  <si>
-    <t>Products-Current_Account-Cheques-Input_Fields-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70838</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Create_New_Recipient_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70839</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Modify_Data_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70840</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-In_Future_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70841</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_DATE_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70842</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_DATE-invalid_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70843</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_AMOUNT_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70844</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_AMOUNT-invalid_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70845</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_STATUS_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70846</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Product_On_The_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70847</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70848</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Details-Financial_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70849</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70850</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Annuity_Plan_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70851</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Annuity_Plan-Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70852</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Annuity_Plan-Filter-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70853</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Payments_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70854</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Payments-Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70855</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-CREATE_CONFIRMATION_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70856</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Archive_Payments_Transaction_List_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70857</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Details-Financial_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70858</t>
-  </si>
-  <si>
-    <t>Authentication-Mobile_Login-Logout_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70859</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-Successful_Payment_Via_The_Scan_And_Pay_Option_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70860</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-QR_Code_Not_Recognized_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70861</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-Payment_Via_The_Scan_And_Pay_Option-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70862</t>
-  </si>
-  <si>
-    <t>Mobile_Login-Generate_OTP-mToken_From_Login_Screen_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70863</t>
-  </si>
-  <si>
-    <t>Term_Deposit_Accounts_Details_Financial_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70864</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Confirmation_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70865</t>
-  </si>
-  <si>
-    <t>CURRENT_FOREIGN_ACCOUNTS-TRANSACTIONS-OVERVIEW_BY_DIFFERENT_CURRENCIES_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70866</t>
-  </si>
-  <si>
-    <t>General-Login_Page_Elements-Buttons-Activated_Users_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70867</t>
-  </si>
-  <si>
-    <t>Authentication-Login_In_MOB-Login_Page_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70868</t>
-  </si>
-  <si>
-    <t>Authentication-Login_With_PIN_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70869</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70870</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70871</t>
-  </si>
-  <si>
-    <t>Current_Foreign-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70872</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70873</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70874</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70875</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70876</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Input-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70877</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70878</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Okruzenje</t>
-  </si>
-  <si>
-    <t>Napomena</t>
-  </si>
-  <si>
-    <t>Sanity</t>
-  </si>
-  <si>
-    <t>UAT</t>
-  </si>
-  <si>
-    <t>Oba</t>
-  </si>
-  <si>
-    <t>Pusti test kada proradi placanje da vidis je l rade poslednji koraci</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>Poslednji korak pada. Kada kliknem na drugu valutu, ostaje transakcija sa EUR valutom</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t>Ova dva testa su isto automatizovana</t>
@@ -4229,67 +4280,171 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="11"/>
-      <c r="B101" s="11"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="15"/>
+      <c r="B101" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="11"/>
-      <c r="B102" s="11"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="15"/>
+      <c r="B102" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G102" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="11"/>
-      <c r="B103" s="11"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="15"/>
+      <c r="B103" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="11"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="11"/>
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="15"/>
+      <c r="B104" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G104" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="11"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="11"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="15"/>
+      <c r="B105" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G105" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="11"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="15"/>
+      <c r="B106" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="11"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="15"/>
+      <c r="B107" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G107" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="11"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="15"/>
+      <c r="B108" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G108" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="11"/>
@@ -4708,7 +4863,7 @@
       <c r="F160" s="15"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G100" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G108" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -4734,16 +4889,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -4751,10 +4906,10 @@
         <v>179</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
@@ -4762,13 +4917,13 @@
         <v>205</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
@@ -4776,10 +4931,10 @@
         <v>181</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
@@ -4787,10 +4942,10 @@
         <v>85</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
@@ -4798,10 +4953,10 @@
         <v>183</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D6" s="5"/>
     </row>
@@ -4810,13 +4965,13 @@
         <v>185</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -4824,10 +4979,10 @@
         <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
@@ -4835,10 +4990,10 @@
         <v>67</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
@@ -4846,10 +5001,10 @@
         <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D10" s="7"/>
     </row>
@@ -4858,10 +5013,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:4">
@@ -4869,10 +5024,10 @@
         <v>73</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:4">
@@ -4880,21 +5035,21 @@
         <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>87</v>
+        <v>237</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:4">
@@ -4902,10 +5057,10 @@
         <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:4">
@@ -4913,13 +5068,13 @@
         <v>189</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:4">
@@ -4927,10 +5082,10 @@
         <v>191</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="D17" s="9"/>
     </row>
@@ -4939,10 +5094,10 @@
         <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:4">
@@ -4950,24 +5105,24 @@
         <v>117</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:4">
@@ -4975,10 +5130,10 @@
         <v>81</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:4">
@@ -4986,21 +5141,21 @@
         <v>161</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:4">
@@ -5008,10 +5163,10 @@
         <v>171</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:4">
@@ -5019,10 +5174,10 @@
         <v>113</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:4">
@@ -5030,10 +5185,10 @@
         <v>135</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:4">
@@ -5041,10 +5196,10 @@
         <v>97</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:4">
@@ -5052,10 +5207,10 @@
         <v>125</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:4">
@@ -5063,10 +5218,10 @@
         <v>175</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:4">
@@ -5074,10 +5229,10 @@
         <v>177</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:4">
@@ -5085,10 +5240,10 @@
         <v>207</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D31" s="7"/>
     </row>
@@ -5097,13 +5252,13 @@
         <v>193</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:4">
@@ -5111,10 +5266,10 @@
         <v>195</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D33" s="7"/>
     </row>
@@ -5123,10 +5278,10 @@
         <v>197</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:4">
@@ -5134,10 +5289,10 @@
         <v>199</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:4">
@@ -5145,10 +5300,10 @@
         <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:4">
@@ -5156,10 +5311,10 @@
         <v>201</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:4">
@@ -5167,10 +5322,10 @@
         <v>19</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:4">
@@ -5178,10 +5333,10 @@
         <v>203</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="281">
   <si>
     <t>App</t>
   </si>
@@ -72,228 +72,228 @@
     <t>data</t>
   </si>
   <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>Product_Summary-Loan_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70780</t>
+  </si>
+  <si>
+    <t>Product_Summary_Sorting_on_the_Product_Summary_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70781</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70782</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_6</t>
+  </si>
+  <si>
+    <t>C70783</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_2</t>
+  </si>
+  <si>
+    <t>C70784</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_3</t>
+  </si>
+  <si>
+    <t>C70785</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_4</t>
+  </si>
+  <si>
+    <t>C70786</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_5</t>
+  </si>
+  <si>
+    <t>C70787</t>
+  </si>
+  <si>
+    <t>Current_Accounts-Transactions_Details-Create_Confirmation_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70788</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Search_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70789</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70790</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70791</t>
+  </si>
+  <si>
+    <t>Product_Summary_Edit_Product_View_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70792</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70793</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70794</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70795</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70797</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Current_Foreign_Account</t>
+  </si>
+  <si>
+    <t>C70798</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Credit_Card</t>
+  </si>
+  <si>
+    <t>C70799</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Savings_Account</t>
+  </si>
+  <si>
+    <t>C70800</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Term_Deposit_Accounts</t>
+  </si>
+  <si>
+    <t>C70801</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Loan_Accounts</t>
+  </si>
+  <si>
+    <t>C70802</t>
+  </si>
+  <si>
+    <t>Product_Summary-Term_Deposits_Lists_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70803</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts_Transactions_Filter_By_Date_CustomDateRange_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70804</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts_Transactions_Details_Transaction_Confirmation_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70805</t>
+  </si>
+  <si>
+    <t>Current_Accounts_Transactions_Details_Transaction_Confirmation_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70806</t>
+  </si>
+  <si>
+    <t>Product_Summary-Current_Domestic_Accounts-List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70807</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70808</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70809</t>
+  </si>
+  <si>
+    <t>Product_Summary-Savings_Accounts_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70810</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Details_Card_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70811</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70812</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Date-Predefined_Date_Range_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70813</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Product_Details-Financial-Details_Is_Not_Visible_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70814</t>
+  </si>
+  <si>
+    <t>Product_Summary-Credit_Card_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70815</t>
+  </si>
+  <si>
+    <t>Term_Deposit_Accounts_Details_Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70816</t>
+  </si>
+  <si>
     <t>on</t>
   </si>
   <si>
-    <t>Product_Summary-Loan_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70780</t>
-  </si>
-  <si>
-    <t>off</t>
-  </si>
-  <si>
-    <t>Product_Summary_Sorting_on_the_Product_Summary_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70781</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70782</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_6</t>
-  </si>
-  <si>
-    <t>C70783</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_2</t>
-  </si>
-  <si>
-    <t>C70784</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_3</t>
-  </si>
-  <si>
-    <t>C70785</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_4</t>
-  </si>
-  <si>
-    <t>C70786</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_5</t>
-  </si>
-  <si>
-    <t>C70787</t>
-  </si>
-  <si>
-    <t>Current_Accounts-Transactions_Details-Create_Confirmation_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70788</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Search_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70789</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70790</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70791</t>
-  </si>
-  <si>
-    <t>Product_Summary_Edit_Product_View_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70792</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70793</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70794</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70795</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Current_Domestic_Account</t>
-  </si>
-  <si>
-    <t>C70797</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Current_Foreign_Account</t>
-  </si>
-  <si>
-    <t>C70798</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Credit_Card</t>
-  </si>
-  <si>
-    <t>C70799</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Savings_Account</t>
-  </si>
-  <si>
-    <t>C70800</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Term_Deposit_Accounts</t>
-  </si>
-  <si>
-    <t>C70801</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Loan_Accounts</t>
-  </si>
-  <si>
-    <t>C70802</t>
-  </si>
-  <si>
-    <t>Product_Summary-Term_Deposits_Lists_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70803</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts_Transactions_Filter_By_Date_CustomDateRange_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70804</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts_Transactions_Details_Transaction_Confirmation_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70805</t>
-  </si>
-  <si>
-    <t>Current_Accounts_Transactions_Details_Transaction_Confirmation_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70806</t>
-  </si>
-  <si>
-    <t>Product_Summary-Current_Domestic_Accounts-List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70807</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70808</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70809</t>
-  </si>
-  <si>
-    <t>Product_Summary-Savings_Accounts_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70810</t>
-  </si>
-  <si>
-    <t>Credit_Cards_Details_Card_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70811</t>
-  </si>
-  <si>
-    <t>Credit_Cards_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70812</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter_By_Date-Predefined_Date_Range_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70813</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Product_Details-Financial-Details_Is_Not_Visible_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70814</t>
-  </si>
-  <si>
-    <t>Product_Summary-Credit_Card_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70815</t>
-  </si>
-  <si>
-    <t>Term_Deposit_Accounts_Details_Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70816</t>
-  </si>
-  <si>
     <t>Term_Deposits_Accounts-Details_[MOB_ANDROID]</t>
   </si>
   <si>
@@ -582,160 +582,268 @@
     <t>C70864</t>
   </si>
   <si>
+    <t>Payments-Domestic_Payments-Confirmation_[MOB_ANDROID]-Internal_Urgent_Payment</t>
+  </si>
+  <si>
+    <t>C70865</t>
+  </si>
+  <si>
+    <t>CURRENT_FOREIGN_ACCOUNTS-TRANSACTIONS-OVERVIEW_BY_DIFFERENT_CURRENCIES_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70866</t>
+  </si>
+  <si>
+    <t>General-Login_Page_Elements-Buttons-Activated_Users_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70867</t>
+  </si>
+  <si>
+    <t>Authentication-Login_In_MOB-Login_Page_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70868</t>
+  </si>
+  <si>
+    <t>Authentication-Login_With_PIN_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70869</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70870</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70871</t>
+  </si>
+  <si>
+    <t>Current_Foreign-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70872</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70873</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70874</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70875</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Internal_Non_Urgent_Payment</t>
+  </si>
+  <si>
+    <t>C70876</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Input-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70877</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70878</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70879</t>
+  </si>
+  <si>
+    <t>CURRENT_ACCOUNTS_RSD-STATEMANTS-FILTER_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70880</t>
+  </si>
+  <si>
+    <t>CURRENT_FOREIGN_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70881</t>
+  </si>
+  <si>
+    <t>SAVINGS_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70882</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-Invalid_Account_Combination_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70883</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-Domestic_Payment_Page_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70884</t>
+  </si>
+  <si>
+    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Debit_Cards</t>
+  </si>
+  <si>
+    <t>C70885</t>
+  </si>
+  <si>
+    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70886</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Transactions_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70887</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Transactions_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70888</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Non_Urgent_Payment_No_Model</t>
+  </si>
+  <si>
+    <t>C70889</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_No_Model</t>
+  </si>
+  <si>
+    <t>C70890</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_11</t>
+  </si>
+  <si>
+    <t>C70891</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_97</t>
+  </si>
+  <si>
+    <t>C70892</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_11-invalid</t>
+  </si>
+  <si>
+    <t>C70893</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_97-invalid</t>
+  </si>
+  <si>
+    <t>C70894</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Non_Urgent_Payment_Model_11</t>
+  </si>
+  <si>
+    <t>C70895</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Non_Urgent_Payment_Model_97</t>
+  </si>
+  <si>
+    <t>C70896</t>
+  </si>
+  <si>
+    <t>Cards-Transactions_Details_[MOB_ANDROID]-Debit_Cards</t>
+  </si>
+  <si>
+    <t>C70897</t>
+  </si>
+  <si>
+    <t>Cards-Transactions_Details_[MOB_ANDROID]-Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70898</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-PAYMENTS_LIST_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70899</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70900</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70901</t>
+  </si>
+  <si>
+    <t>Payments_Upcoming_Payments_List_Of_Transactions_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70902</t>
+  </si>
+  <si>
+    <t>Payments_Upcoming_Payments_Cancel_Payment_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70903</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Okruzenje</t>
+  </si>
+  <si>
+    <t>Napomena</t>
+  </si>
+  <si>
+    <t>Sanity</t>
+  </si>
+  <si>
+    <t>UAT</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>Oba</t>
+  </si>
+  <si>
+    <t>Pusti test kada proradi placanje da vidis je l rade poslednji koraci</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
     <t>Payments-Domestic_Payments-Confirmation_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70865</t>
-  </si>
-  <si>
-    <t>CURRENT_FOREIGN_ACCOUNTS-TRANSACTIONS-OVERVIEW_BY_DIFFERENT_CURRENCIES_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70866</t>
-  </si>
-  <si>
-    <t>General-Login_Page_Elements-Buttons-Activated_Users_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70867</t>
-  </si>
-  <si>
-    <t>Authentication-Login_In_MOB-Login_Page_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70868</t>
-  </si>
-  <si>
-    <t>Authentication-Login_With_PIN_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70869</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70870</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70871</t>
-  </si>
-  <si>
-    <t>Current_Foreign-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70872</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70873</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70874</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70875</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70876</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Input-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70877</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70878</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Payments-Filter-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70879</t>
-  </si>
-  <si>
-    <t>CURRENT_ACCOUNTS_RSD-STATEMANTS-FILTER_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70880</t>
-  </si>
-  <si>
-    <t>CURRENT_FOREIGN_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70881</t>
-  </si>
-  <si>
-    <t>SAVINGS_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70882</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-Invalid_Account_Combination_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70883</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-Domestic_Payment_Page_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70884</t>
-  </si>
-  <si>
-    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Debit_Cards</t>
-  </si>
-  <si>
-    <t>C70885</t>
-  </si>
-  <si>
-    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Credit_Cards</t>
-  </si>
-  <si>
-    <t>C70886</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Okruzenje</t>
-  </si>
-  <si>
-    <t>Napomena</t>
-  </si>
-  <si>
-    <t>Sanity</t>
-  </si>
-  <si>
-    <t>UAT</t>
-  </si>
-  <si>
-    <t>Oba</t>
-  </si>
-  <si>
-    <t>Pusti test kada proradi placanje da vidis je l rade poslednji koraci</t>
-  </si>
-  <si>
-    <t>Critical</t>
   </si>
   <si>
     <t>Poslednji korak pada. Kada kliknem na drugu valutu, ostaje transakcija sa EUR valutom</t>
@@ -1831,15 +1939,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H160"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:G162"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
     <col min="7" max="7" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1862,7 +1970,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
@@ -1885,7 +1993,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="11" t="s">
         <v>7</v>
       </c>
@@ -1907,853 +2015,813 @@
       <c r="G3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="11" t="s">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="C6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="C7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="C8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="C10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="16" t="s">
+      <c r="C11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:7">
+      <c r="A12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:8">
-      <c r="A12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="16" t="s">
+      <c r="C12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="16" t="s">
+      <c r="C13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="C14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="D14" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="C16" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="11" t="s">
+      <c r="C17" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="D19" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="11" t="s">
+      <c r="C20" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="D20" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="11" t="s">
+      <c r="C22" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="11" t="s">
+      <c r="C23" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="11" t="s">
+      <c r="C24" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="D24" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="11" t="s">
+      <c r="C25" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="D25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="11" t="s">
+      <c r="C26" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="D26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="11" t="s">
+      <c r="C27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="D27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="11" t="s">
+      <c r="C28" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="C29" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="D29" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="11"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="D30" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="11" t="s">
+      <c r="C31" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="D31" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="11" t="s">
+      <c r="C32" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="D32" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="11" t="s">
+      <c r="C33" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="D33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="16" t="s">
+      <c r="C34" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="D34" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="16" t="s">
+      <c r="C35" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="D35" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:7">
+      <c r="A36" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:8">
-      <c r="A36" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="16" t="s">
+      <c r="C36" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="D36" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="D37" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="11" t="s">
+      <c r="C38" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="D38" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="11" t="s">
         <v>7</v>
       </c>
@@ -2776,7 +2844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:7">
       <c r="A40" s="11" t="s">
         <v>7</v>
       </c>
@@ -2798,11 +2866,8 @@
       <c r="G40" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="11" t="s">
         <v>7</v>
       </c>
@@ -2825,7 +2890,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" customFormat="1" spans="1:8">
+    <row r="42" customFormat="1" spans="1:7">
       <c r="A42" s="11" t="s">
         <v>7</v>
       </c>
@@ -2847,11 +2912,8 @@
       <c r="G42" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="11" t="s">
         <v>7</v>
       </c>
@@ -2873,11 +2935,8 @@
       <c r="G43" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="11" t="s">
         <v>7</v>
       </c>
@@ -2900,7 +2959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:7">
       <c r="A45" s="11" t="s">
         <v>7</v>
       </c>
@@ -2922,11 +2981,8 @@
       <c r="G45" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="11" t="s">
         <v>7</v>
       </c>
@@ -2948,11 +3004,8 @@
       <c r="G46" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H46" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="11" t="s">
         <v>7</v>
       </c>
@@ -2974,11 +3027,8 @@
       <c r="G47" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H47" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="11" t="s">
         <v>7</v>
       </c>
@@ -3000,11 +3050,8 @@
       <c r="G48" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="11" t="s">
         <v>7</v>
       </c>
@@ -3026,11 +3073,8 @@
       <c r="G49" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H49" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="11" t="s">
         <v>7</v>
       </c>
@@ -3052,11 +3096,8 @@
       <c r="G50" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H50" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="11" t="s">
         <v>7</v>
       </c>
@@ -3078,11 +3119,8 @@
       <c r="G51" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H51" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="11" t="s">
         <v>7</v>
       </c>
@@ -3105,7 +3143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:7">
       <c r="A53" s="11" t="s">
         <v>7</v>
       </c>
@@ -3127,11 +3165,8 @@
       <c r="G53" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H53" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="11" t="s">
         <v>7</v>
       </c>
@@ -3154,7 +3189,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:7">
       <c r="A55" s="11" t="s">
         <v>7</v>
       </c>
@@ -3176,11 +3211,8 @@
       <c r="G55" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H55" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="11" t="s">
         <v>7</v>
       </c>
@@ -3202,11 +3234,8 @@
       <c r="G56" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H56" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="11" t="s">
         <v>7</v>
       </c>
@@ -3228,11 +3257,8 @@
       <c r="G57" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H57" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="11" t="s">
         <v>7</v>
       </c>
@@ -3255,7 +3281,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:7">
       <c r="A59" s="11" t="s">
         <v>7</v>
       </c>
@@ -3277,11 +3303,8 @@
       <c r="G59" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H59" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="11" t="s">
         <v>7</v>
       </c>
@@ -3303,11 +3326,8 @@
       <c r="G60" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H60" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -3329,11 +3349,8 @@
       <c r="G61" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="11" t="s">
         <v>7</v>
       </c>
@@ -3356,7 +3373,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:7">
       <c r="A63" s="11" t="s">
         <v>7</v>
       </c>
@@ -3379,7 +3396,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:7">
       <c r="A64" s="11" t="s">
         <v>7</v>
       </c>
@@ -3401,11 +3418,8 @@
       <c r="G64" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H64" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" s="11" t="s">
         <v>7</v>
       </c>
@@ -3427,11 +3441,8 @@
       <c r="G65" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H65" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="11" t="s">
         <v>7</v>
       </c>
@@ -3453,11 +3464,8 @@
       <c r="G66" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H66" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="11" t="s">
         <v>7</v>
       </c>
@@ -3479,11 +3487,8 @@
       <c r="G67" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H67" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" s="11" t="s">
         <v>7</v>
       </c>
@@ -3505,11 +3510,8 @@
       <c r="G68" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H68" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="11" t="s">
         <v>7</v>
       </c>
@@ -3531,11 +3533,8 @@
       <c r="G69" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H69" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" s="11" t="s">
         <v>7</v>
       </c>
@@ -3557,11 +3556,8 @@
       <c r="G70" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H70" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" s="11" t="s">
         <v>7</v>
       </c>
@@ -3583,11 +3579,8 @@
       <c r="G71" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H71" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" s="11" t="s">
         <v>7</v>
       </c>
@@ -3609,11 +3602,8 @@
       <c r="G72" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H72" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" s="11" t="s">
         <v>7</v>
       </c>
@@ -3635,11 +3625,8 @@
       <c r="G73" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H73" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" s="11" t="s">
         <v>7</v>
       </c>
@@ -3661,11 +3648,8 @@
       <c r="G74" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H74" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" s="11" t="s">
         <v>7</v>
       </c>
@@ -3687,11 +3671,8 @@
       <c r="G75" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H75" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" s="11" t="s">
         <v>7</v>
       </c>
@@ -3714,7 +3695,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:7">
       <c r="A77" s="11" t="s">
         <v>7</v>
       </c>
@@ -3736,11 +3717,8 @@
       <c r="G77" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H77" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" s="11" t="s">
         <v>7</v>
       </c>
@@ -3762,11 +3740,8 @@
       <c r="G78" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H78" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" s="11" t="s">
         <v>7</v>
       </c>
@@ -3788,11 +3763,8 @@
       <c r="G79" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H79" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" s="11" t="s">
         <v>7</v>
       </c>
@@ -3812,10 +3784,10 @@
         <v>12</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" s="11" t="s">
         <v>7</v>
       </c>
@@ -3838,7 +3810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:7">
       <c r="A82" s="11" t="s">
         <v>7</v>
       </c>
@@ -3860,11 +3832,8 @@
       <c r="G82" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H82" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" s="11" t="s">
         <v>7</v>
       </c>
@@ -3887,7 +3856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:7">
       <c r="A84" s="11" t="s">
         <v>7</v>
       </c>
@@ -3910,7 +3879,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:7">
       <c r="A85" s="11" t="s">
         <v>7</v>
       </c>
@@ -3930,10 +3899,10 @@
         <v>12</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" s="11" t="s">
         <v>7</v>
       </c>
@@ -3953,10 +3922,10 @@
         <v>12</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" s="11" t="s">
         <v>7</v>
       </c>
@@ -3976,10 +3945,10 @@
         <v>12</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" s="11" t="s">
         <v>7</v>
       </c>
@@ -3999,10 +3968,10 @@
         <v>12</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" s="11" t="s">
         <v>7</v>
       </c>
@@ -4025,7 +3994,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:7">
       <c r="A90" s="11" t="s">
         <v>7</v>
       </c>
@@ -4048,7 +4017,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:7">
       <c r="A91" s="11" t="s">
         <v>7</v>
       </c>
@@ -4071,7 +4040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:7">
       <c r="A92" s="11" t="s">
         <v>7</v>
       </c>
@@ -4094,7 +4063,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:7">
       <c r="A93" s="11" t="s">
         <v>7</v>
       </c>
@@ -4117,7 +4086,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:7">
       <c r="A94" s="11" t="s">
         <v>7</v>
       </c>
@@ -4140,7 +4109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:7">
       <c r="A95" s="11" t="s">
         <v>7</v>
       </c>
@@ -4163,7 +4132,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:7">
       <c r="A96" s="11" t="s">
         <v>7</v>
       </c>
@@ -4229,7 +4198,7 @@
         <v>12</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4275,7 +4244,7 @@
         <v>12</v>
       </c>
       <c r="G100" s="11" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4448,141 +4417,362 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="11"/>
-      <c r="B109" s="11"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="15"/>
+      <c r="B109" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="11"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="15"/>
+      <c r="B110" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="11"/>
-      <c r="B111" s="11"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="15"/>
+      <c r="B111" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="11"/>
-      <c r="B112" s="11"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="11"/>
-      <c r="E112" s="11"/>
-      <c r="F112" s="15"/>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="B112" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G112" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" s="11"/>
-      <c r="B113" s="11"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="11"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="15"/>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="B113" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" s="11"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="11"/>
-      <c r="E114" s="11"/>
-      <c r="F114" s="15"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="B114" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" s="11"/>
-      <c r="B115" s="11"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="11"/>
-      <c r="E115" s="11"/>
-      <c r="F115" s="15"/>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="B115" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" s="11"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="15"/>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="B116" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E116" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G116" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" s="11"/>
-      <c r="B117" s="11"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="11"/>
-      <c r="E117" s="11"/>
-      <c r="F117" s="15"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="B117" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E117" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G117" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" s="11"/>
-      <c r="B118" s="11"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="15"/>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="B118" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" s="11"/>
-      <c r="B119" s="11"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="15"/>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="B119" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G119" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" s="11"/>
-      <c r="B120" s="11"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="11"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="15"/>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="B120" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G120" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" s="11"/>
-      <c r="B121" s="11"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="11"/>
-      <c r="E121" s="11"/>
-      <c r="F121" s="15"/>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="B121" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G121" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" s="11"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="11"/>
-      <c r="E122" s="11"/>
-      <c r="F122" s="15"/>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="B122" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G122" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" s="11"/>
-      <c r="B123" s="11"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="11"/>
-      <c r="E123" s="11"/>
-      <c r="F123" s="15"/>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="B123" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E123" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G123" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" s="11"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="11"/>
-      <c r="E124" s="11"/>
-      <c r="F124" s="15"/>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="B124" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G124" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" s="11"/>
-      <c r="B125" s="11"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="11"/>
-      <c r="E125" s="11"/>
-      <c r="F125" s="15"/>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="B125" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G125" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" s="11"/>
       <c r="B126" s="11"/>
       <c r="C126" s="11"/>
@@ -4590,7 +4780,7 @@
       <c r="E126" s="11"/>
       <c r="F126" s="15"/>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:7">
       <c r="A127" s="11"/>
       <c r="B127" s="11"/>
       <c r="C127" s="11"/>
@@ -4598,7 +4788,7 @@
       <c r="E127" s="11"/>
       <c r="F127" s="15"/>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:7">
       <c r="A128" s="11"/>
       <c r="B128" s="11"/>
       <c r="C128" s="11"/>
@@ -4862,8 +5052,24 @@
       <c r="E160" s="11"/>
       <c r="F160" s="15"/>
     </row>
+    <row r="161" spans="1:6">
+      <c r="A161" s="11"/>
+      <c r="B161" s="11"/>
+      <c r="C161" s="11"/>
+      <c r="D161" s="11"/>
+      <c r="E161" s="11"/>
+      <c r="F161" s="15"/>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="11"/>
+      <c r="B162" s="11"/>
+      <c r="C162" s="11"/>
+      <c r="D162" s="11"/>
+      <c r="E162" s="11"/>
+      <c r="F162" s="15"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G108" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G125" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -4889,16 +5095,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -4906,24 +5112,24 @@
         <v>179</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>205</v>
+        <v>266</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
@@ -4931,32 +5137,32 @@
         <v>181</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="D6" s="5"/>
     </row>
@@ -4965,13 +5171,13 @@
         <v>185</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -4979,32 +5185,32 @@
         <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="D10" s="7"/>
     </row>
@@ -5013,43 +5219,43 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:4">
@@ -5057,10 +5263,10 @@
         <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:4">
@@ -5068,13 +5274,13 @@
         <v>189</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:4">
@@ -5082,10 +5288,10 @@
         <v>191</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="D17" s="9"/>
     </row>
@@ -5094,10 +5300,10 @@
         <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:4">
@@ -5105,35 +5311,35 @@
         <v>117</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:4">
@@ -5141,21 +5347,21 @@
         <v>161</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:4">
@@ -5163,10 +5369,10 @@
         <v>171</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:4">
@@ -5174,10 +5380,10 @@
         <v>113</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:4">
@@ -5185,10 +5391,10 @@
         <v>135</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:4">
@@ -5196,10 +5402,10 @@
         <v>97</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:4">
@@ -5207,10 +5413,10 @@
         <v>125</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:4">
@@ -5218,10 +5424,10 @@
         <v>175</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:4">
@@ -5229,10 +5435,10 @@
         <v>177</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:4">
@@ -5240,10 +5446,10 @@
         <v>207</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="D31" s="7"/>
     </row>
@@ -5252,13 +5458,13 @@
         <v>193</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:4">
@@ -5266,10 +5472,10 @@
         <v>195</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="D33" s="7"/>
     </row>
@@ -5278,10 +5484,10 @@
         <v>197</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:4">
@@ -5289,21 +5495,21 @@
         <v>199</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:4">
@@ -5311,21 +5517,21 @@
         <v>201</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:4">
@@ -5333,10 +5539,10 @@
         <v>203</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8340"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$149</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="330">
   <si>
     <t>App</t>
   </si>
@@ -955,6 +955,12 @@
   </si>
   <si>
     <t>C70926</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[MOB_ANDROID]-View_And_Repeat</t>
+  </si>
+  <si>
+    <t>C70927</t>
   </si>
   <si>
     <t>Name</t>
@@ -1715,7 +1721,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1759,7 +1765,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2106,10 +2111,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="112.574074074074" customWidth="1"/>
-    <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
+    <col min="2" max="2" width="112.571428571429" customWidth="1"/>
+    <col min="4" max="5" width="10.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:7">
@@ -5518,12 +5523,24 @@
     </row>
     <row r="149" customFormat="1" spans="1:7">
       <c r="A149" s="13"/>
-      <c r="B149" s="13"/>
-      <c r="C149" s="13"/>
-      <c r="D149" s="13"/>
-      <c r="E149" s="13"/>
-      <c r="F149" s="15"/>
-      <c r="G149" s="19"/>
+      <c r="B149" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="D149" s="13">
+        <v>3</v>
+      </c>
+      <c r="E149" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G149" s="17" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="150" customFormat="1" spans="1:7">
       <c r="A150" s="13"/>
@@ -5532,7 +5549,7 @@
       <c r="D150" s="13"/>
       <c r="E150" s="13"/>
       <c r="F150" s="15"/>
-      <c r="G150" s="19"/>
+      <c r="G150" s="13"/>
     </row>
     <row r="151" customFormat="1" spans="1:7">
       <c r="A151" s="13"/>
@@ -5541,7 +5558,7 @@
       <c r="D151" s="13"/>
       <c r="E151" s="13"/>
       <c r="F151" s="15"/>
-      <c r="G151" s="19"/>
+      <c r="G151" s="13"/>
     </row>
     <row r="152" customFormat="1" spans="1:7">
       <c r="A152" s="13"/>
@@ -5550,7 +5567,7 @@
       <c r="D152" s="13"/>
       <c r="E152" s="13"/>
       <c r="F152" s="15"/>
-      <c r="G152" s="19"/>
+      <c r="G152" s="13"/>
     </row>
     <row r="153" customFormat="1" spans="1:7">
       <c r="A153" s="13"/>
@@ -5559,7 +5576,7 @@
       <c r="D153" s="13"/>
       <c r="E153" s="13"/>
       <c r="F153" s="15"/>
-      <c r="G153" s="19"/>
+      <c r="G153" s="13"/>
     </row>
     <row r="154" customFormat="1" spans="1:7">
       <c r="A154" s="13"/>
@@ -5568,7 +5585,7 @@
       <c r="D154" s="13"/>
       <c r="E154" s="13"/>
       <c r="F154" s="15"/>
-      <c r="G154" s="19"/>
+      <c r="G154" s="13"/>
     </row>
     <row r="155" customFormat="1" spans="1:7">
       <c r="A155" s="13"/>
@@ -5577,7 +5594,7 @@
       <c r="D155" s="13"/>
       <c r="E155" s="13"/>
       <c r="F155" s="15"/>
-      <c r="G155" s="19"/>
+      <c r="G155" s="13"/>
     </row>
     <row r="156" customFormat="1" spans="1:7">
       <c r="A156" s="13"/>
@@ -5586,7 +5603,7 @@
       <c r="D156" s="13"/>
       <c r="E156" s="13"/>
       <c r="F156" s="15"/>
-      <c r="G156" s="19"/>
+      <c r="G156" s="13"/>
     </row>
     <row r="157" customFormat="1" spans="1:7">
       <c r="A157" s="13"/>
@@ -5595,7 +5612,7 @@
       <c r="D157" s="13"/>
       <c r="E157" s="13"/>
       <c r="F157" s="15"/>
-      <c r="G157" s="19"/>
+      <c r="G157" s="13"/>
     </row>
     <row r="158" customFormat="1" spans="1:7">
       <c r="A158" s="13"/>
@@ -5604,7 +5621,7 @@
       <c r="D158" s="13"/>
       <c r="E158" s="13"/>
       <c r="F158" s="15"/>
-      <c r="G158" s="19"/>
+      <c r="G158" s="13"/>
     </row>
     <row r="159" customFormat="1" spans="1:7">
       <c r="A159" s="13"/>
@@ -5613,7 +5630,7 @@
       <c r="D159" s="13"/>
       <c r="E159" s="13"/>
       <c r="F159" s="15"/>
-      <c r="G159" s="19"/>
+      <c r="G159" s="13"/>
     </row>
     <row r="160" customFormat="1" spans="1:7">
       <c r="A160" s="13"/>
@@ -5622,7 +5639,7 @@
       <c r="D160" s="13"/>
       <c r="E160" s="13"/>
       <c r="F160" s="15"/>
-      <c r="G160" s="19"/>
+      <c r="G160" s="13"/>
     </row>
     <row r="161" customFormat="1" spans="1:7">
       <c r="A161" s="13"/>
@@ -5631,7 +5648,7 @@
       <c r="D161" s="13"/>
       <c r="E161" s="13"/>
       <c r="F161" s="15"/>
-      <c r="G161" s="19"/>
+      <c r="G161" s="13"/>
     </row>
     <row r="162" customFormat="1" spans="1:7">
       <c r="A162" s="13"/>
@@ -5640,10 +5657,10 @@
       <c r="D162" s="13"/>
       <c r="E162" s="13"/>
       <c r="F162" s="15"/>
-      <c r="G162" s="19"/>
+      <c r="G162" s="13"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G81" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G149" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B128">
@@ -5717,10 +5734,10 @@
   <conditionalFormatting sqref="B148">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C148">
+  <conditionalFormatting sqref="C148:C149">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C127 C133 C149:C1048576">
+  <conditionalFormatting sqref="C1:C127;C133;C150:C1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5732,27 +5749,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="101.666666666667" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="8.88888888888889" style="1" collapsed="1"/>
-    <col min="3" max="3" width="10.1111111111111" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="8.88571428571429" style="1" collapsed="1"/>
+    <col min="3" max="3" width="10.1142857142857" style="1" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="123" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="16384" width="8.88888888888889" style="1" collapsed="1"/>
+    <col min="5" max="16384" width="8.88571428571429" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -5760,24 +5777,24 @@
         <v>178</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
       <c r="A3" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
@@ -5785,10 +5802,10 @@
         <v>180</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
@@ -5796,21 +5813,21 @@
         <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="D6" s="5"/>
     </row>
@@ -5819,13 +5836,13 @@
         <v>184</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -5833,10 +5850,10 @@
         <v>90</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
@@ -5844,10 +5861,10 @@
         <v>66</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
@@ -5855,10 +5872,10 @@
         <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D10" s="7"/>
     </row>
@@ -5867,10 +5884,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:4">
@@ -5878,10 +5895,10 @@
         <v>72</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:4">
@@ -5889,21 +5906,21 @@
         <v>58</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:4">
@@ -5911,10 +5928,10 @@
         <v>186</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:4">
@@ -5922,13 +5939,13 @@
         <v>188</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:4">
@@ -5936,10 +5953,10 @@
         <v>190</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D17" s="9"/>
     </row>
@@ -5948,10 +5965,10 @@
         <v>132</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:4">
@@ -5959,24 +5976,24 @@
         <v>116</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:4">
@@ -5984,10 +6001,10 @@
         <v>80</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:4">
@@ -5995,21 +6012,21 @@
         <v>160</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:4">
       <c r="A23" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:4">
@@ -6017,10 +6034,10 @@
         <v>170</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:4">
@@ -6028,10 +6045,10 @@
         <v>112</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:4">
@@ -6039,10 +6056,10 @@
         <v>134</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:4">
@@ -6050,10 +6067,10 @@
         <v>96</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:4">
@@ -6061,10 +6078,10 @@
         <v>124</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:4">
@@ -6072,10 +6089,10 @@
         <v>174</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:4">
@@ -6083,10 +6100,10 @@
         <v>176</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:4">
@@ -6094,25 +6111,25 @@
         <v>206</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D31" s="7"/>
     </row>
-    <row r="32" s="1" customFormat="1" ht="28.8" spans="1:4">
+    <row r="32" s="1" customFormat="1" ht="45" spans="1:4">
       <c r="A32" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:4">
@@ -6120,10 +6137,10 @@
         <v>194</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D33" s="7"/>
     </row>
@@ -6132,10 +6149,10 @@
         <v>196</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:4">
@@ -6143,10 +6160,10 @@
         <v>198</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:4">
@@ -6154,10 +6171,10 @@
         <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:4">
@@ -6165,10 +6182,10 @@
         <v>200</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:4">
@@ -6176,10 +6193,10 @@
         <v>18</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:4">
@@ -6187,10 +6204,10 @@
         <v>202</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
